--- a/1_Correlation_r_Z/r_&_Z_values.xlsx
+++ b/1_Correlation_r_Z/r_&_Z_values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data_Pro\New_Analysis\Verif_Cluster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Spatio-Temporal_Strategies\1_Correlation_r_Z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F97E284-8711-4FBE-B6B7-9B1AE97F01CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58160AA3-BE74-486A-9E0E-52932DF0A780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{C5E97854-7CF4-4414-A117-D5DC08AFE5A9}"/>
+    <workbookView xWindow="25260" yWindow="150" windowWidth="25905" windowHeight="20820" xr2:uid="{C5E97854-7CF4-4414-A117-D5DC08AFE5A9}"/>
   </bookViews>
   <sheets>
     <sheet name="r" sheetId="1" r:id="rId1"/>
@@ -244,31 +244,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -286,6 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACFBA03-7687-42A2-8BF1-5B7BF9566A60}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -628,27 +624,23 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="21">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
         <v>29</v>
       </c>
       <c r="B2" s="3">
@@ -660,14 +652,13 @@
       <c r="D2" s="4">
         <v>0.30704510432676702</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="17"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>50</v>
       </c>
       <c r="B3" s="6">
@@ -679,14 +670,13 @@
       <c r="D3" s="7">
         <v>0.414824029154992</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="17"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
         <v>37</v>
       </c>
       <c r="B4" s="6">
@@ -698,14 +688,13 @@
       <c r="D4" s="7">
         <v>0.75465377842222303</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="17"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>41</v>
       </c>
       <c r="B5" s="6">
@@ -717,14 +706,13 @@
       <c r="D5" s="7">
         <v>0.51630266317617901</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>27</v>
       </c>
       <c r="B6" s="6">
@@ -736,14 +724,13 @@
       <c r="D6" s="7">
         <v>0.17387847370217499</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="17"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>14</v>
       </c>
       <c r="B7" s="6">
@@ -755,14 +742,13 @@
       <c r="D7" s="7">
         <v>0.47784576980266202</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>16</v>
       </c>
       <c r="B8" s="6">
@@ -774,14 +760,13 @@
       <c r="D8" s="7">
         <v>0.60438697534132302</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>10</v>
       </c>
       <c r="B9" s="6">
@@ -793,14 +778,13 @@
       <c r="D9" s="7">
         <v>0.54397042348457803</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>20</v>
       </c>
       <c r="B10" s="6">
@@ -812,14 +796,13 @@
       <c r="D10" s="7">
         <v>0.63758448832960601</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>19</v>
       </c>
       <c r="B11" s="6">
@@ -831,14 +814,13 @@
       <c r="D11" s="7">
         <v>0.80543574397925399</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20">
         <v>44</v>
       </c>
       <c r="B12" s="9">
@@ -850,14 +832,13 @@
       <c r="D12" s="10">
         <v>0.70794537397773105</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
         <v>26</v>
       </c>
       <c r="B13" s="3">
@@ -869,14 +850,13 @@
       <c r="D13" s="4">
         <v>0.63553836469885605</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>38</v>
       </c>
       <c r="B14" s="6">
@@ -888,14 +868,13 @@
       <c r="D14" s="7">
         <v>0.80053799857561203</v>
       </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="17"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
         <v>17</v>
       </c>
       <c r="B15" s="6">
@@ -907,14 +886,13 @@
       <c r="D15" s="7">
         <v>0.74047184325529303</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="17"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>33</v>
       </c>
       <c r="B16" s="6">
@@ -926,14 +904,13 @@
       <c r="D16" s="7">
         <v>0.57955960882971802</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>21</v>
       </c>
       <c r="B17" s="6">
@@ -945,14 +922,13 @@
       <c r="D17" s="7">
         <v>0.48394708451489599</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="17"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>32</v>
       </c>
       <c r="B18" s="6">
@@ -964,14 +940,13 @@
       <c r="D18" s="7">
         <v>0.66926568039525003</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="17"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>42</v>
       </c>
       <c r="B19" s="6">
@@ -983,14 +958,13 @@
       <c r="D19" s="7">
         <v>0.76866328523510097</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="17"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="22">
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>46</v>
       </c>
       <c r="B20" s="6">
@@ -1002,14 +976,13 @@
       <c r="D20" s="7">
         <v>0.85332148489317206</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="17"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
         <v>30</v>
       </c>
       <c r="B21" s="6">
@@ -1021,14 +994,13 @@
       <c r="D21" s="7">
         <v>0.74010331065508494</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="17"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
         <v>13</v>
       </c>
       <c r="B22" s="6">
@@ -1040,14 +1012,13 @@
       <c r="D22" s="7">
         <v>0.80238840482068097</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="17"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="22">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
         <v>45</v>
       </c>
       <c r="B23" s="6">
@@ -1059,14 +1030,13 @@
       <c r="D23" s="7">
         <v>0.70180463592605702</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="17"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23">
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20">
         <v>11</v>
       </c>
       <c r="B24" s="9">
@@ -1078,14 +1048,13 @@
       <c r="D24" s="10">
         <v>0.67855323459628802</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="17"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
         <v>31</v>
       </c>
       <c r="B25" s="3">
@@ -1097,14 +1066,13 @@
       <c r="D25" s="4">
         <v>0.706713664544389</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="17"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
         <v>39</v>
       </c>
       <c r="B26" s="6">
@@ -1116,14 +1084,13 @@
       <c r="D26" s="7">
         <v>0.71583090868579602</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="17"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="22">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>43</v>
       </c>
       <c r="B27" s="6">
@@ -1135,14 +1102,13 @@
       <c r="D27" s="7">
         <v>0.66031685223494596</v>
       </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="17"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="22">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
         <v>40</v>
       </c>
       <c r="B28" s="6">
@@ -1154,14 +1120,13 @@
       <c r="D28" s="7">
         <v>0.57355003739925403</v>
       </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="17"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
         <v>25</v>
       </c>
       <c r="B29" s="6">
@@ -1173,14 +1138,13 @@
       <c r="D29" s="7">
         <v>0.71389845393142004</v>
       </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="17"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="22">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
         <v>18</v>
       </c>
       <c r="B30" s="6">
@@ -1192,14 +1156,13 @@
       <c r="D30" s="7">
         <v>0.66156115718939101</v>
       </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="17"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="22">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
         <v>36</v>
       </c>
       <c r="B31" s="6">
@@ -1211,14 +1174,13 @@
       <c r="D31" s="7">
         <v>0.76242258414238295</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="17"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="22">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
         <v>12</v>
       </c>
       <c r="B32" s="6">
@@ -1230,14 +1192,13 @@
       <c r="D32" s="7">
         <v>0.88353699747323799</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="17"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="22">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
         <v>35</v>
       </c>
       <c r="B33" s="6">
@@ -1249,14 +1210,13 @@
       <c r="D33" s="7">
         <v>0.79150150630827099</v>
       </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="17"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="23">
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="20">
         <v>24</v>
       </c>
       <c r="B34" s="9">
@@ -1268,22 +1228,14 @@
       <c r="D34" s="10">
         <v>0.81274277928368899</v>
       </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="17"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J13:J24">
-    <sortCondition ref="J13:J24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G34">
+    <sortCondition ref="G2:G34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1291,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6560312D-CD1E-4AFD-8009-E21A4B9BA3EF}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -1299,7 +1251,7 @@
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1312,672 +1264,535 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>29</v>
       </c>
       <c r="B2" s="2">
         <v>-0.69346800240045303</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>0.24484253525427199</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>0.31727965568977001</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="17"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>50</v>
       </c>
       <c r="B3" s="5">
         <v>-0.59888570061353597</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3">
         <v>0.248213443046819</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>0.44142391723012597</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="17"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>37</v>
       </c>
       <c r="B4" s="5">
         <v>-0.58471680874044196</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4">
         <v>-0.111823788956673</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>0.98367823844997904</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="17"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>41</v>
       </c>
       <c r="B5" s="5">
         <v>-0.55469280970463497</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5">
         <v>0.31616131066659597</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.57128540909967895</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="17"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>27</v>
       </c>
       <c r="B6" s="5">
         <v>-0.49841601949286402</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6">
         <v>0.81054596189986605</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>0.175663295664203</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>14</v>
       </c>
       <c r="B7" s="5">
         <v>-0.47996273947080698</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7">
         <v>0.30317670752600401</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>0.52018887053253604</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="17"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>16</v>
       </c>
       <c r="B8" s="5">
         <v>-0.38070308333886899</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8">
         <v>0.40065589034944299</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>0.70003024638042299</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="17"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>10</v>
       </c>
       <c r="B9" s="5">
         <v>-0.37250571388306603</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9">
         <v>0.497485613697706</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>0.60977745321827903</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="17"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>20</v>
       </c>
       <c r="B10" s="5">
         <v>-0.37191940431857401</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10">
         <v>3.6429860307518498E-2</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>0.75409309311477202</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="17"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>19</v>
       </c>
       <c r="B11" s="5">
         <v>-0.35693425789868199</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11">
         <v>-2.2599056414377299E-2</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>1.11389738869702</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="17"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>44</v>
       </c>
       <c r="B12" s="5">
         <v>-0.34957941648760299</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12">
         <v>0.21869953170436299</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>0.88305276559892198</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="17"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>26</v>
       </c>
       <c r="B13" s="5">
         <v>-0.120190708452804</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13">
         <v>0.492996887922868</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>0.75065300560713399</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="17"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>38</v>
       </c>
       <c r="B14" s="5">
         <v>-8.7384018097375296E-2</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14">
         <v>0.24004503760787901</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>1.10010851909299</v>
       </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="17"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>17</v>
       </c>
       <c r="B15" s="5">
         <v>-8.4867686106905496E-2</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15">
         <v>0.35188185572998798</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>0.95152316458956399</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="17"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>33</v>
       </c>
       <c r="B16" s="5">
         <v>-3.19266432327696E-2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16">
         <v>0.78719576391264101</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>0.66179932312117196</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="17"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>21</v>
       </c>
       <c r="B17" s="5">
         <v>-2.46440117349708E-2</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17">
         <v>0.57475869794779999</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>0.52812572807157099</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="17"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>32</v>
       </c>
       <c r="B18" s="5">
         <v>3.8263460762727602E-2</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18">
         <v>0.50474453037412803</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>0.80941185155099304</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="17"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>42</v>
       </c>
       <c r="B19" s="5">
         <v>4.8652499687114402E-2</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19">
         <v>0.51548372787990304</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>1.0170525226515199</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46</v>
       </c>
       <c r="B20" s="5">
         <v>7.4840328791843602E-2</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20">
         <v>0.319031799101957</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>1.26824574285614</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="17"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>30</v>
       </c>
       <c r="B21" s="5">
         <v>8.2059194604555394E-2</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21">
         <v>0.59454703347791205</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>0.95070778050374705</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="17"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>13</v>
       </c>
       <c r="B22" s="5">
         <v>9.8647597933957304E-2</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22">
         <v>0.559934403582384</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>1.1052822461295999</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="17"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>45</v>
       </c>
       <c r="B23" s="5">
         <v>0.11538039531902899</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23">
         <v>0.67409567463825804</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>0.87084783084897699</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="17"/>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>11</v>
       </c>
       <c r="B24" s="5">
         <v>0.191226477463699</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24">
         <v>0.78723531984668804</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>0.82642779173744196</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="17"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>31</v>
       </c>
       <c r="B25" s="5">
         <v>0.27149605158303503</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25">
         <v>0.98337655391914802</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>0.88058779043770596</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="17"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>39</v>
       </c>
       <c r="B26" s="5">
         <v>0.27372827910776099</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26">
         <v>0.95293622336523998</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>0.89904164209683102</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="17"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>43</v>
       </c>
       <c r="B27" s="5">
         <v>0.27722055568506998</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27">
         <v>1.09682860212636</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>0.79337523660518405</v>
       </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="17"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>40</v>
       </c>
       <c r="B28" s="5">
         <v>0.2835474498833</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28">
         <v>1.38468523597353</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <v>0.65279723849792604</v>
       </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="17"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>25</v>
       </c>
       <c r="B29" s="5">
         <v>0.30230710067170802</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29">
         <v>0.75814819611638695</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13">
         <v>0.89508952416782295</v>
       </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="17"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>18</v>
       </c>
       <c r="B30" s="5">
         <v>0.33675923672430103</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30">
         <v>1.1393573323427999</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13">
         <v>0.79558474533637802</v>
       </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="17"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>36</v>
       </c>
       <c r="B31" s="5">
         <v>0.402333746365032</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31">
         <v>0.98097221225986997</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13">
         <v>1.0019755389821801</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="17"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>12</v>
       </c>
       <c r="B32" s="5">
         <v>0.41177393233542697</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32">
         <v>0.77475808838238802</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="13">
         <v>1.3916665110931601</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="17"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>35</v>
       </c>
       <c r="B33" s="5">
         <v>0.41799096507192401</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33">
         <v>0.97046063891727197</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="13">
         <v>1.0754387804201999</v>
       </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="17"/>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>24</v>
       </c>
       <c r="B34" s="8">
         <v>0.47785875578433101</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <v>0.65294353243860104</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="15">
         <v>1.1350565706964999</v>
       </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="17"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F34">

--- a/1_Correlation_r_Z/r_&_Z_values.xlsx
+++ b/1_Correlation_r_Z/r_&_Z_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Spatio-Temporal_Strategies\1_Correlation_r_Z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58160AA3-BE74-486A-9E0E-52932DF0A780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020B2E0D-E80B-4A78-A0FB-338E3CA17679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25260" yWindow="150" windowWidth="25905" windowHeight="20820" xr2:uid="{C5E97854-7CF4-4414-A117-D5DC08AFE5A9}"/>
+    <workbookView xWindow="25245" yWindow="60" windowWidth="25905" windowHeight="20820" xr2:uid="{C5E97854-7CF4-4414-A117-D5DC08AFE5A9}"/>
   </bookViews>
   <sheets>
     <sheet name="r" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -281,7 +281,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,8 +651,6 @@
       <c r="D2" s="4">
         <v>0.30704510432676702</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
     </row>
@@ -670,8 +667,6 @@
       <c r="D3" s="7">
         <v>0.414824029154992</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
     </row>
@@ -688,8 +683,6 @@
       <c r="D4" s="7">
         <v>0.75465377842222303</v>
       </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
     </row>
@@ -706,8 +699,6 @@
       <c r="D5" s="7">
         <v>0.51630266317617901</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
@@ -724,8 +715,6 @@
       <c r="D6" s="7">
         <v>0.17387847370217499</v>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
@@ -742,8 +731,6 @@
       <c r="D7" s="7">
         <v>0.47784576980266202</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
     </row>
@@ -760,8 +747,6 @@
       <c r="D8" s="7">
         <v>0.60438697534132302</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
     </row>
@@ -778,8 +763,6 @@
       <c r="D9" s="7">
         <v>0.54397042348457803</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
     </row>
@@ -796,8 +779,6 @@
       <c r="D10" s="7">
         <v>0.63758448832960601</v>
       </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
     </row>
@@ -814,8 +795,6 @@
       <c r="D11" s="7">
         <v>0.80543574397925399</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
     </row>
@@ -832,8 +811,6 @@
       <c r="D12" s="10">
         <v>0.70794537397773105</v>
       </c>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
       <c r="J12" s="16"/>
       <c r="K12" s="16"/>
     </row>
@@ -850,8 +827,6 @@
       <c r="D13" s="4">
         <v>0.63553836469885605</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
     </row>
@@ -868,8 +843,6 @@
       <c r="D14" s="7">
         <v>0.80053799857561203</v>
       </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
     </row>
@@ -886,8 +859,6 @@
       <c r="D15" s="7">
         <v>0.74047184325529303</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
     </row>
@@ -904,8 +875,6 @@
       <c r="D16" s="7">
         <v>0.57955960882971802</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
       <c r="J16" s="16"/>
       <c r="K16" s="16"/>
     </row>
@@ -922,8 +891,6 @@
       <c r="D17" s="7">
         <v>0.48394708451489599</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
     </row>
@@ -940,8 +907,6 @@
       <c r="D18" s="7">
         <v>0.66926568039525003</v>
       </c>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
     </row>
@@ -958,8 +923,6 @@
       <c r="D19" s="7">
         <v>0.76866328523510097</v>
       </c>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
       <c r="J19" s="16"/>
       <c r="K19" s="16"/>
     </row>
@@ -976,8 +939,6 @@
       <c r="D20" s="7">
         <v>0.85332148489317206</v>
       </c>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
       <c r="J20" s="16"/>
       <c r="K20" s="16"/>
     </row>
@@ -994,8 +955,6 @@
       <c r="D21" s="7">
         <v>0.74010331065508494</v>
       </c>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
       <c r="J21" s="16"/>
       <c r="K21" s="16"/>
     </row>
@@ -1012,8 +971,6 @@
       <c r="D22" s="7">
         <v>0.80238840482068097</v>
       </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
     </row>
@@ -1030,8 +987,6 @@
       <c r="D23" s="7">
         <v>0.70180463592605702</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
       <c r="J23" s="16"/>
       <c r="K23" s="16"/>
     </row>
@@ -1048,8 +1003,6 @@
       <c r="D24" s="10">
         <v>0.67855323459628802</v>
       </c>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
       <c r="J24" s="16"/>
       <c r="K24" s="16"/>
     </row>
@@ -1066,8 +1019,6 @@
       <c r="D25" s="4">
         <v>0.706713664544389</v>
       </c>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
@@ -1084,8 +1035,6 @@
       <c r="D26" s="7">
         <v>0.71583090868579602</v>
       </c>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
       <c r="J26" s="16"/>
       <c r="K26" s="16"/>
     </row>
@@ -1102,8 +1051,6 @@
       <c r="D27" s="7">
         <v>0.66031685223494596</v>
       </c>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
       <c r="J27" s="16"/>
       <c r="K27" s="16"/>
     </row>
@@ -1120,8 +1067,6 @@
       <c r="D28" s="7">
         <v>0.57355003739925403</v>
       </c>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
     </row>
@@ -1138,8 +1083,6 @@
       <c r="D29" s="7">
         <v>0.71389845393142004</v>
       </c>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
     </row>
@@ -1156,8 +1099,6 @@
       <c r="D30" s="7">
         <v>0.66156115718939101</v>
       </c>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
       <c r="J30" s="16"/>
       <c r="K30" s="16"/>
     </row>
@@ -1174,8 +1115,6 @@
       <c r="D31" s="7">
         <v>0.76242258414238295</v>
       </c>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
       <c r="J31" s="16"/>
       <c r="K31" s="16"/>
     </row>
@@ -1192,8 +1131,6 @@
       <c r="D32" s="7">
         <v>0.88353699747323799</v>
       </c>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
     </row>
@@ -1210,8 +1147,6 @@
       <c r="D33" s="7">
         <v>0.79150150630827099</v>
       </c>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
       <c r="J33" s="16"/>
       <c r="K33" s="16"/>
     </row>
@@ -1228,8 +1163,6 @@
       <c r="D34" s="10">
         <v>0.81274277928368899</v>
       </c>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
       <c r="J34" s="16"/>
       <c r="K34" s="16"/>
     </row>
